--- a/output-report/2027_report_2day.xlsx
+++ b/output-report/2027_report_2day.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\jackk\Workspace-jack\report\04-apply3-status-antigravity\output-report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D77CE8-4A18-46FD-810A-221130B45D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC4FE98-F81A-4610-B6FB-738DB2FBCACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2일차1월5일(화)17시" sheetId="1" r:id="rId1"/>
@@ -4905,8 +4905,8 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="27" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="29" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="45" min="1" max="14" man="1"/>
   </rowBreaks>
